--- a/output/北塩原村_MECE_利用の流れと報酬改定.xlsx
+++ b/output/北塩原村_MECE_利用の流れと報酬改定.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>制度名称の表記が混在している。障害支援区分（6件）と障害児入所支援（5件）は法令表記で統一されている一方、障害児通所支援は法令4件・村表記11件、障害児相談支援は法令3件・村表記12件である。第5章1（5）では⑤障害児入所支援と⑥障がい児相談支援が同じ並びで食い違う。全編に及ぶ編集方針であり、当方だけでは決められないため他メンバーに諮る（Ｓ-25）。</t>
+          <t>制度名称の表記が混在している。障害支援区分（６件）と障害児入所支援（５件）は法令表記で統一されている一方、障害児通所支援は法令4件・村表記11件、障害児相談支援は法令3件・村表記12件である。第5章1（5）では⑤障害児入所支援と⑥障がい児相談支援が同じ並びで食い違う。全編に及ぶ編集方針であり、当方だけでは決められないため他メンバーに諮る（Ｓ-25）。</t>
         </is>
       </c>
     </row>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>計画冒頭の注記は「法律用語や施設名等の固有名称を除き、可能な限り『害』の字をひらがなで表記」としている。正本では障害支援区分（6件）・障害児入所支援（5件）は法令表記で統一されている一方、障害児通所支援は法令表記4件・村表記11件、障害児相談支援は法令表記3件・村表記12件と混在している。第5章1（5）では⑤障害児入所支援と⑥障がい児相談支援が同じ並びの中で食い違っている。①給付・制度・区分の正式名称はすべて法令表記にする②村の編集方針として制度名称も村表記に統一するのいずれかに決めたい。当方の追記は決まった方に合わせる</t>
+          <t>計画冒頭の注記は「法律用語や施設名等の固有名称を除き、可能な限り『害』の字をひらがなで表記」としている。正本では障害支援区分（６件）・障害児入所支援（５件）は法令表記で統一されている一方、障害児通所支援は法令表記４件・村表記11件、障害児相談支援は法令表記３件・村表記12件と混在している。第5章1（5）では⑤障害児入所支援と⑥障がい児相談支援が同じ並びの中で食い違っている。①給付・制度・区分の正式名称はすべて法令表記にする②村の編集方針として制度名称も村表記に統一するのいずれかに決めたい。当方の追記は決まった方に合わせる</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
